--- a/erp-server/erp-server-file/src/main/resources/excel/scm/cfgSupplierSalesExport.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/scm/cfgSupplierSalesExport.xlsx
@@ -71,7 +71,7 @@
     <t>{.dailySalesTypeName}</t>
   </si>
   <si>
-    <t>{.salesRatio}</t>
+    <t>{.salesRatioStr}</t>
   </si>
   <si>
     <t>{.noticeEnabledName}</t>
